--- a/branches/release/2027.0.0-ballot/ValueSet-mii-vs-mikrobio-empfindlichkeit-phenotyp-loinc.xlsx
+++ b/branches/release/2027.0.0-ballot/ValueSet-mii-vs-mikrobio-empfindlichkeit-phenotyp-loinc.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot2</t>
   </si>
   <si>
     <t>Name</t>
